--- a/n8n_simulation_results.xlsx
+++ b/n8n_simulation_results.xlsx
@@ -486,1663 +486,1627 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>149760764875</t>
+          <t>149834574934</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Instruments Rents</t>
+          <t>SECOND Hand Shuttering &amp; Scaffolding Material</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Musical Instrument Rental</t>
+          <t>Scaffolding Accessories</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"Instrument Type":"Manual","Musical Instrument Type":"Guitar","Number of Items":"1","Usage/Application":"Parties"}</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>{"Application":"Shuttering","Diameter":"12 mm","Length":"3 m","Quantity":"500","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch, isq_filled_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
+          <t>Title mentions material, mcat is accessories; ISQ answers not relevant to mcat.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17707540262</t>
+          <t>23763553991</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Instruments Rents</t>
+          <t>Second hand old centering plates</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/QO/OY/IMOB-53893422/img_20171106_004138_114-jpg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2021/7/IE/UC/AS/86514144/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"Instrument Type":"Manual","Musical Instrument Type":"Guitar","Number of Items":"1","Usage/Application":"Parties"}</t>
+          <t>{"Application":"Shuttering","Diameter":"12 mm","Length":"3 m","Quantity":"500","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>149771263646</t>
+          <t>149811072763</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pizza Stone</t>
+          <t>Pharmaceutical Tablet</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pizza Makeline</t>
+          <t>Mifepristone Misoprostol Tablet</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"I am interested in":"Pizza Makeline","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Commercial Use"}</t>
+          <t>{"Composition":"Mifepristone+Miso","Packaging Size":"50 Tablets","Quantity":"2","Quantity Unit":"Box","Strength":"40 mg","Usage/Application":"Distribution"}</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.68).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.67).</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24511610497</t>
+          <t>2856325208888</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12mm Industrial Pizza Stone</t>
+          <t>Auvelity, 45 - 105 MG Extended Release Tablet USA DELIVERY</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/1/IW/WN/VI/113068156/12mm-industrial-pizza-stone.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/4/500905916/FA/EV/PI/243324734/whatsapp-image-2025-03-17-at-11-32-33-abc8f7bd.jpg</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"I am interested in":"Pizza Makeline","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Commercial Use"}</t>
+          <t>{"Composition":"Mifepristone+Miso","Packaging Size":"50 Tablets","Quantity":"2","Quantity Unit":"Box","Strength":"40 mg","Usage/Application":"Distribution"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>149792637952</t>
+          <t>149840285267</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glock 17 Generation 3 CO2 Air Pistol</t>
+          <t>PVR Karizma Zmr Body Kit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Pistol</t>
+          <t>Hero Bike Body Kit</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{"Brand":"Glock","Caliber":"0.177 in (4.5 mm)","Power Source":"CO2"}</t>
+          <t>{"Buyer Filled Details":"White","Model Variant":"Latest","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.65).</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2855577864012</t>
+          <t>21031038091</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Glock 17 Generation 3 Co2 Air Pistol</t>
+          <t>PVR Karizma ZMR Body Kit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/1/478549776/QJ/UV/UM/238257630/hair-pin.jpg</t>
+          <t>http://5.imimg.com/data5/ZJ/BJ/TF/SELLER-12994953/pvr-karizma-zmr-body-kit.jpg</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"Brand":"Glock","Caliber":"0.177 in (4.5 mm)","Power Source":"CO2"}</t>
+          <t>{"Buyer Filled Details":"White","Model Variant":"Latest","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>149759854663</t>
+          <t>149824882159</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Loading Vehicle Mat</t>
+          <t>Gift Hamper Box</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Automotive Floor Mats</t>
+          <t>Gift Hamper</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>{"Material":"Rubber","Quantity":"1","Quantity Unit":"Piece","Width":"40 cm"}</t>
+          <t>{"Application":"Return Gift","Buyer Filled Details":"Pvc","Hamper Type":"Empty","Quantity":"10","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14840703530</t>
+          <t>2857490982091</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Loading Vehicle Mat</t>
+          <t>Gift Hamper Box</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/JE/CA/MY-29521459/vehicle-mat.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/9/543140614/QJ/JP/TY/14715484/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"Material":"Rubber","Quantity":"1","Quantity Unit":"Piece","Width":"40 cm"}</t>
+          <t>{"Application":"Return Gift","Buyer Filled Details":"Pvc","Hamper Type":"Empty","Quantity":"10","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>149748190359</t>
+          <t>149838275759</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pregabalin Capsules 300 mg 15 Capsules</t>
+          <t>Sri Lakshmi Ganesh Silver Coin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pregabalin Capsules &amp; Tablets</t>
+          <t>Ganesh Silver Coin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{"Dosage Form":"Capsule","Quantity":"1","Quantity Unit":"Box","Quantity per Strip":"15 Capsules","Strength":"300 mg"}</t>
+          <t>{"Quantity":"10000","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.82).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.87).</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2859050586512</t>
+          <t>2855310388462</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Signalcure-300</t>
+          <t>Sri Lakshmi Ganesh Silver Coin</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2026/4/597029991/QD/WU/IW/241893436/product-jpeg.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/11/466517809/VS/JX/FN/151479974/prod-20241119-1401298101406463427860710-jpg.jpg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"Dosage Form":"Capsule","Quantity":"1","Quantity Unit":"Box","Quantity per Strip":"15 Capsules","Strength":"300 mg"}</t>
+          <t>{"Quantity":"10000","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>149763247367</t>
+          <t>149847718767</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fiber Car Spoiler</t>
+          <t>ME Mixer Grinder Body</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Car Spoiler</t>
+          <t>Mixer Grinder Body Set</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{"Material":"Fiber","Spoiler Style":"Batman","Vehicle Model":"Ford Fiesta titanium"}</t>
+          <t>{"Body Material":"Fresh Plastic","Buyer Filled Details":"Bonymix","Motor Fit (Watt)":"550 W","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.68).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.9).</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22409503591</t>
+          <t>23952097455</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ABS Car Spoiler</t>
+          <t>ME Mixer Grinder Body</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/OI/SV/WC/SELLER-23286675/abs-car-spoiler.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/10/UP/LY/LI/119556433/me-mixer-grinder-body.jpg</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"Material":"Fiber","Spoiler Style":"Batman","Vehicle Model":"Ford Fiesta titanium"}</t>
+          <t>{"Body Material":"Fresh Plastic","Buyer Filled Details":"Bonymix","Motor Fit (Watt)":"550 W","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>149754376675</t>
+          <t>149825318859</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steel Pawali</t>
+          <t>7 Star Premium Quality Basmati Rice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stainless Steel Drums</t>
+          <t>Basmati Rice</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{"Material Grade":"SS 202","Quantity":"10000","Quantity Unit":"KG","Storage Capacity":"500 Litre","Thickness":"1.2 mm"}</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Packaging Size":"25 kg","Quantity":"16","Quantity Unit":"Kg","Rice Type":"White Sella","Usage/Application":"Food Service","Variety":"1401"}</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.49). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.49</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12529961733</t>
+          <t>24291041562</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Steel Pawali</t>
+          <t>7 Star Premium Quality Basmati Rice</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/TX/ER/MY-29715845/pawali.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/6/DU/RJ/AX/55308823/whatsapp-image-2022-06-03-at-11-12-00-am.jpeg</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"Material Grade":"SS 202","Quantity":"10000","Quantity Unit":"KG","Storage Capacity":"500 Litre","Thickness":"1.2 mm"}</t>
+          <t>{"Packaging Size":"25 kg","Quantity":"16","Quantity Unit":"Kg","Rice Type":"White Sella","Usage/Application":"Food Service","Variety":"1401"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>149802064552</t>
+          <t>149828369695</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>850 SMD Machine Normal Motherboard</t>
+          <t>5 Inch Big Thunder Dragon Condom</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SMD Rework Station</t>
+          <t>Dragon Condom</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>{"Brand":"Quick"}</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Color":"Brown","Length":"5 inch","Quantity":"2","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.47). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.75).</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2859088025648</t>
+          <t>2857824324097</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>850 SMD Machine Normal Motherboard</t>
+          <t>7 inch Big Thunder Dragon Condom</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/4/603181675/BJ/AY/OA/267397848/smd-machine-850-normal-mother-board.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/11/557107226/QG/SD/NB/253279123/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"Brand":"Quick"}</t>
+          <t>{"Color":"Brown","Length":"5 inch","Quantity":"2","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>149785959913</t>
+          <t>149866573467</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IFB 7 Kg Front Load Inner Drum</t>
+          <t>Waller Bracket 50 X 50mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IFB Washing Machine</t>
+          <t>Metal Brackets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>{"Application":"Domestic","Brand":"IFB","Capacity":"7 kg"}</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.32). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Quantity":"400","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2856280565312</t>
+          <t>2850833889962</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ifb 7 Kg Front Load Inner Drum</t>
+          <t>Waller Bracket 50 x 50mm</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/3/498566686/ZD/TX/TC/221789184/ifb-7-kg-front-load-inner-drum.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/4/301521383/UB/SQ/LK/121219085/weller-clamp.jpg</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"Application":"Domestic","Brand":"IFB","Capacity":"7 kg"}</t>
+          <t>{"Quantity":"400","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>149780801185</t>
+          <t>149818255095</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zapata Flyboard</t>
+          <t>Dairy Farm Labour Supplier</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jet Ski</t>
+          <t>Labour Contractors</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{"Material":"Mild Steel","Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.5). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Industry":"Agricultural","Job Role":"Mistri"}</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25367566155</t>
+          <t>2852175563830</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Zapata Flyboard</t>
+          <t>Dairy Farm Labour Supplier</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/3/UN/RG/CI/25642998/zapata-flyboard.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/12/470342423/KA/UF/LY/195968651/dairy-farm-labour-supplier.jpg</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"Material":"Mild Steel","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Industry":"Agricultural","Job Role":"Mistri"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>149742842575</t>
+          <t>149846270675</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>75W Kenstar Air Cooler Motor</t>
+          <t>Costimised Acrylic Leather Box, Rectangular</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cooler Motor</t>
+          <t>Acrylic Boxes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{"Motor Type":"Desert Type","Quantity":"1","Quantity Unit":"Piece","Stack Height":"25 mm","Winding Material":"Copper"}</t>
+          <t>{"Length":"10 inch","Quantity":"10","Quantity Unit":"piece","Shape":"Rectangular","Thickness":"6 mm"}</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.76).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.71).</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2776458888</t>
+          <t>2857296113030</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>75W Kenstar Air Cooler Motor</t>
+          <t>Acrylic Leather Box</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/3/493201239/JR/WD/ST/3744895/geysers.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/8/537613133/JL/GX/NJ/25282342/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"Motor Type":"Desert Type","Quantity":"1","Quantity Unit":"Piece","Stack Height":"25 mm","Winding Material":"Copper"}</t>
+          <t>{"Length":"10 inch","Quantity":"10","Quantity Unit":"piece","Shape":"Rectangular","Thickness":"6 mm"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>149797524863</t>
+          <t>149856947167</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unwanted Kit Tablets Mankind</t>
+          <t>Armature Winding Machine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mifepristone Misoprostol Tablet</t>
+          <t>Armature Coil Winding Machine</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"1 tablet","Composition":"Mifepristone","Packaging Size":"5 tablets","Packaging Type":"Combi-pack Kit","Quantity":"1","Quantity Unit":"Kit"}</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.51). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.9).</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2853672126855</t>
+          <t>1961087430</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Unwanted Kit Tablets Mankind</t>
+          <t>Armature Winding Machine</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2024/3/401642527/FP/JM/VT/88641814/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/UY/LZ/PR/SELLER-1959923/armature-winding.jpg</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"1 tablet","Composition":"Mifepristone","Packaging Size":"5 tablets","Packaging Type":"Combi-pack Kit","Quantity":"1","Quantity Unit":"Kit"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>149778220852</t>
+          <t>149864726167</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tobacco Pouch</t>
+          <t>Tractor Speedometer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tobacco Pouches</t>
+          <t>Speedometer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Buyer Filled Details":"Mahindra &amp; Mahindra 265 DI","Display Type":"Analog &amp; Digital","Quantity":"1","Quantity Unit":"piece"}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.97).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.72).</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23844519862</t>
+          <t>15136284797</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Tobacco Pouch</t>
+          <t>Tractor Speedometer</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2021/8/ZK/CL/DV/78263226/whatsapp-image-2021-08-23-at-1-53-09-pm.jpeg</t>
+          <t>http://5.imimg.com/data5/RM/VH/MY-11540870/tractor-speedometer.jpg</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Buyer Filled Details":"Mahindra &amp; Mahindra 265 DI","Display Type":"Analog &amp; Digital","Quantity":"1","Quantity Unit":"piece"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>149793942146</t>
+          <t>149837621034</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ECM Tester Mr Can Solutions</t>
+          <t>Laptop Packaging Carton Box</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Car Scanner</t>
+          <t>Carton Box</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{"Operating Voltage":"12V","Software Update Period":"Lifetime","Usage/Application":"Workshop Use"}</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.28). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.73).</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2856922242962</t>
+          <t>2853930744133</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ECM TESTER MR CAN Solutions</t>
+          <t>Laptop Packaging Carton Box</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/7/528388360/LJ/WL/MI/38764756/car-engine-control-module.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/411982769/ZL/MN/EA/211679461/laptop-packaging-corrugated-carton-box.jpeg</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"Operating Voltage":"12V","Software Update Period":"Lifetime","Usage/Application":"Workshop Use"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>149751215395</t>
+          <t>149839153067</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hiring of Banana Tree for Wedding Ceremony</t>
+          <t>Stand Fan Rental Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Plants Rental Services</t>
+          <t>Electrical Equipment Rental</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{"Dimensions":"12 inch"}</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.27). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Fan Type":"Stand Fan","Quantity":"5","Quantity Unit":"Day"}</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8757007962</t>
+          <t>23108344833</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hiring of Banana Tree for Wedding Ceremony</t>
+          <t>Pedestal Fan Rental Service</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>http://3.imimg.com/data3/VH/RI/MY-10555023/banana-tree.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/2/391539244/IA/WV/VW/9602217/pedestal-fan-rental-service.jpg</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"Dimensions":"12 inch"}</t>
+          <t>{"Fan Type":"Stand Fan","Quantity":"5","Quantity Unit":"Day"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>149784884763</t>
+          <t>149848219113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18 Inch Alloy Wheels</t>
+          <t>Bolero Maxitruck Plus Di Turbo Engine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Alloy Wheels</t>
+          <t>Utility Trucks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>{"Quantity":"5000","Quantity Unit":"Set","Vehicle Brand":"Tata","Vehicle Model":"Tiago","Wheel Size":"18 inch"}</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.83).</t>
+          <t>Title describes engine, mcat is trucks category.</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.83</v>
+        <v>0.27</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22866971855</t>
+          <t>13822804130</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15 Inch Alloy Wheels</t>
+          <t>Bolero Maxitruck Plus Di Turbo Engine</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2020/11/JQ/VX/RY/18902895/product-jpeg.jpg</t>
+          <t>http://4.imimg.com/data4/QM/HP/GLADMIN-4480501/1.jpg</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"Quantity":"5000","Quantity Unit":"Set","Vehicle Brand":"Tata","Vehicle Model":"Tiago","Wheel Size":"18 inch"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>149789141352</t>
+          <t>149867422795</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>300ml Mineral Water</t>
+          <t>Poco Refurbished Mobile Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mineral Water Bottle</t>
+          <t>Refurbished Mobile Phones</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"First quality"}</t>
+          <t>{"Buyer Filled Details":"Kis condition mein hai, I phone 7plus"}</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.76).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.74).</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25699286455</t>
+          <t>2853762536197</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>300ml Mineral Water</t>
+          <t>Poco Refurbished Mobile Phone</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2022/12/FX/WI/CE/4208987/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/409684385/WD/CG/EU/29989742/oneplus-6-refurbished-mobile-phone.jpg</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"First quality"}</t>
+          <t>{"Buyer Filled Details":"Kis condition mein hai, I phone 7plus"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>149743456295</t>
+          <t>149861469175</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ration Rice</t>
+          <t>Maktab Bag</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Parboiled Rice</t>
+          <t>Tool Bags</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>{"Broken Ratio":"50%","Cleaning Process":"Sortex","I am interested in":"Parboiled Rice","Processing Type":"Raw","Quantity":"5","Quantity Unit":"Kg","Usage/Application":"Food Service"}</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.89).</t>
+          <t>Title describes a school bag, but mcat lists tool bags.</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2858771519333</t>
+          <t>2857909678530</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ration rice</t>
+          <t>Maktab Bag</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IMOB/Default/2026/2/581927245/UQ/TL/OH/202098002/17704600180277016647187105171154-1770460046104-jpg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/11/560397898/YU/NY/UC/205749628/product-jpeg.jpeg</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"Broken Ratio":"50%","Cleaning Process":"Sortex","I am interested in":"Parboiled Rice","Processing Type":"Raw","Quantity":"5","Quantity Unit":"Kg","Usage/Application":"Food Service"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>149748786363</t>
+          <t>149816108395</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Display Counter</t>
+          <t>ABB Achm-01c Charging Control Board</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Food &amp; Bakery Display Counter</t>
+          <t>ABB Interface Board</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Heated","Cooling Type":"Non-Refrigerated","Length":"4 ft","Number of Shelves":"3 Shelves","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.68).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.62).</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2850055259848</t>
+          <t>2850948425988</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Display Counter</t>
+          <t>ABB ACHM-01C CHARGING CONTROL BOARD</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/2/UY/EX/IX/184351030/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/4/303154028/ID/SS/PY/10222995/abb-achm-01c-charging-control-board.jpeg</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Heated","Cooling Type":"Non-Refrigerated","Length":"4 ft","Number of Shelves":"3 Shelves","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>149797538513</t>
+          <t>149794606959</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paynearby Distributor ID</t>
+          <t>Bright Yellow Crude Sulphur Granules</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Atm Cards</t>
+          <t>Sulphur Granules</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"I am interested in":"Atm Cards"}</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Brand":"Reliance","Buyer Filled Details":"Buyer requires yellow flakes.","Packaging Size":"50 kg","Purity":"99.5%","Quantity":"20","Quantity Unit":"Tonne"}</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.31). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.86).</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.31</v>
+        <v>0.86</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22342238512</t>
+          <t>26161212991</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paynearby Distributor Id</t>
+          <t>Bright Yellow Crude Sulphur Granules</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/5/421054154/JH/PV/LW/37545398/paynearby-distributor-retailer-id.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/9/SH/FF/MJ/67740578/bright-yellow-crude-sulphur-granules.jpeg</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"I am interested in":"Atm Cards"}</t>
+          <t>{"Brand":"Reliance","Buyer Filled Details":"Buyer requires yellow flakes.","Packaging Size":"50 kg","Purity":"99.5%","Quantity":"20","Quantity Unit":"Tonne"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>149797892075</t>
+          <t>149826909534</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Whirlpool Fridge Freezer Box Cabinet</t>
+          <t>Hero Green Luster</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Refrigerator Cabinets</t>
+          <t>Metal Polishing Compounds</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"Number of Doors":"Single Door","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.86).</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>21001011833</t>
+          <t>2852802806862</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Whirlpool Fridge Freezer Box Cabinet</t>
+          <t>Hero Green Luster</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/10/461537352/UF/IB/WB/34049678/whirlpool-fridge-freezer-box-cabinet.webp</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/10/456548260/KL/FO/ID/5057661/hero-gren-luster.jpeg</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"Number of Doors":"Single Door","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>149788582052</t>
+          <t>149820415852</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Digital Pedometer Step Counter</t>
+          <t>CARWASHING Machine Pump Rubber Seal Kit in Coimbatore</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Digital Step Counter</t>
+          <t>Seal Kit</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece","Why do you need this":"For Reselling"}</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>{"Buyer Filled Details":"Karcher car washing machine, Pressure washers","Quantity":"01","Quantity Unit":"Kit"}</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>isq_filled_title_mismatch, isq_filled_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.9).</t>
+          <t>Buyer details irrelevant to product title and category.</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20413766755</t>
+          <t>2854606703673</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Omron Pedometer HJ-325</t>
+          <t>CARWASHING MACHINE PUMP RUBBER SEAL KIT IN COIMBATORE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/1/JZ/OK/HR/8455524/omron-pedometer-hj-325.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/8/441018276/ST/EN/IJ/5996328/seal-kit.jpeg</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece","Why do you need this":"For Reselling"}</t>
+          <t>{"Buyer Filled Details":"Karcher car washing machine, Pressure washers","Quantity":"01","Quantity Unit":"Kit"}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>149787721595</t>
+          <t>149851604285</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Apple iPhone Se 32 Gb Grey Color</t>
+          <t>Godrej 950 Washing Machine Spin Lid</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apple iPhone</t>
+          <t>Washing Machine Spin Cap</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.88).</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22551720633</t>
+          <t>20609493562</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Apple Iphone SE 32 GB Grey Color</t>
+          <t>Godrej 950 Washing Machine Spin Lid</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2020/8/ZO/JI/MD/33076508/39d80523-eddf-44b3-981c-ea561fdb8130-jpg.jpg</t>
+          <t>https://5.imimg.com/data5/QR/LU/JR/SELLER-6242229/washing-machine-spin-lid.jpg</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>149749908785</t>
+          <t>149863307867</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Corporate / Call Center Pickup &amp; Drop Services</t>
+          <t>Cardboard Sheet for Masala Packaging</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pick Up Service</t>
+          <t>Corrugated Packaging Sheet</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Buyer Filled Details":"Soory ye hai pin code 249403","Form":"Sheet","GSM":"250 GSM","No. Of Ply":"3 Ply","Quantity":"500","Quantity Unit":"Kg"}</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.6). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.71).</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8043394855</t>
+          <t>2859273294097</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Corporate / Call Center Pickup &amp; Drop Services</t>
+          <t>Cardboard Sheet For Masala Packaging</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>http://3.imimg.com/data3/FR/TS/MY-10936853/images-callcenter.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2026/5/609526941/IM/VS/LZ/79083048/product.jpg</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Buyer Filled Details":"Soory ye hai pin code 249403","Form":"Sheet","GSM":"250 GSM","No. Of Ply":"3 Ply","Quantity":"500","Quantity Unit":"Kg"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>149775137275</t>
+          <t>149810541113</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cotton Shirt Pant Set</t>
+          <t>Stainless Steel Knife Pen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pant Shirt Combo Pack</t>
+          <t>Stainless Steel Knife</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{"Brand":"Raymond","Packaging Type":"Box Packing","Quantity":"2","Quantity Unit":"Set"}</t>
+          <t>{"Buyer Filled Details":"Knife wala pen","Quantity":"2","Quantity Unit":"Piece","Size":"12 inch (30 cm)"}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.7).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.92).</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2852638291191</t>
+          <t>25998740788</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cotton Shirt Pant Set</t>
+          <t>Stainless Steel Knife Pen</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/10/351318911/WD/PS/HE/104792729/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/5/309767724/AL/QR/MS/14841028/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"Brand":"Raymond","Packaging Type":"Box Packing","Quantity":"2","Quantity Unit":"Set"}</t>
+          <t>{"Buyer Filled Details":"Knife wala pen","Quantity":"2","Quantity Unit":"Piece","Size":"12 inch (30 cm)"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>149804580875</t>
+          <t>149869442059</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fabric Katta Pai</t>
+          <t>N Kol</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PP Woven Sack Fabric</t>
+          <t>Cough Syrup</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>{"Filter Type":"Box Filter"}</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch, isq_filled_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.61).</t>
+          <t>Title and mcat differ; ISQ answer irrelevant to mcat.</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>21308448748</t>
+          <t>2856532781488</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fabric Katta Pai</t>
+          <t>N Kol</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SY/ND/YJ/SELLER-83884298/fabric-katta-pai.png</t>
+          <t>http://5.imimg.com/data5/NSDMERP/Default/2025/5/511579938/PD/EK/NS/96809804/96809804-product-1747482529931.png</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Filter Type":"Box Filter"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>149798736067</t>
+          <t>149850867346</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ghar Shop Magic Shop</t>
+          <t>Power Tiller Seat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bath Soaps</t>
+          <t>Power Tiller Parts</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>{"Brand":"Mysore Sandal"}</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Compatible Brand":"VST Shakti","Fuel Type":"Diesel","Horsepower":"12 HP","Quantity":"5000","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.1). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.77).</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2855746515662</t>
+          <t>2857514134762</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ghar Shop Magic Shop</t>
+          <t>Power Tiller Seat</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2025/2/486861013/DB/AV/QP/161582673/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/9/544285038/VH/HX/HR/37621677/product-jpeg.jpeg</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"Brand":"Mysore Sandal"}</t>
+          <t>{"Compatible Brand":"VST Shakti","Fuel Type":"Diesel","Horsepower":"12 HP","Quantity":"5000","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>149806818285</t>
+          <t>149819818059</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5 kg Dynamix Cow Ghee Tin</t>
+          <t>Jute Leadis Siders Bags</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cow Ghee</t>
+          <t>Side Bag</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{"Packaging Size":"5 kg","Packaging Type":"Tin","Quantity":"20","Quantity Unit":"Kg"}</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
+          <t>Title mentions 'Siders Bags', mcat 'Side Bag' mismatch.</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20672375233</t>
+          <t>2852763288891</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5 Ltr Dynamix Cow Ghee Tin</t>
+          <t>Jute leadis siders bags</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/AQ/CE/QP/SELLER-28324032/5-ltr-dynamix-cow-ghee-tin.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/10/356598575/PV/AY/MR/135428123/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"Packaging Size":"5 kg","Packaging Type":"Tin","Quantity":"20","Quantity Unit":"Kg"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>149750229785</t>
+          <t>149843769563</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boss Dd3t Digital Delay</t>
+          <t>Mens Half Pant</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Guitar Accessories</t>
+          <t>Men Bermudas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{"Material":"Stainless Steel","Quantity":"10000","Quantity Unit":"piece","Type of Parts":"Digital Delay"}</t>
+          <t>{"Fabric":"Cotton","Pattern":"Plain","Quantity":"2","Quantity Unit":"Piece","Size":"XL"}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2152,172 +2116,176 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.04). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>Title describes half pants, category lists bermudas—different product types.</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2851599661055</t>
+          <t>2849107111597</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Boss DD3T Digital Delay</t>
+          <t>Mens Half Pant</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/3/404030397/OI/DR/WI/191821988/boss-dd3t-digital-delay.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/12/AK/FH/UX/64202968/half-pant.jpg</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"Material":"Stainless Steel","Quantity":"10000","Quantity Unit":"piece","Type of Parts":"Digital Delay"}</t>
+          <t>{"Fabric":"Cotton","Pattern":"Plain","Quantity":"2","Quantity Unit":"Piece","Size":"XL"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>149746956485</t>
+          <t>149837602552</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>X6 Retro Pandora Box Controllers Arcade Video Game Machine</t>
+          <t>360degre Rotate Light</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Arcade Game</t>
+          <t>LED Rotating Bulb</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"The buyer is requesting the price of the engine part for the machine.","Country of Origin":"India","Game Name":"Catch the Baton","Operation Mode":"Coin Operated"}</t>
+          <t>{"Dimensions":"360","Quantity":"1","Quantity Unit":"Unit(s)"}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.64).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2858919896848</t>
+          <t>2855559647212</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X6 Retro Pandora Box Controllers Arcade Video Game Machine</t>
+          <t>360degre rotate light</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/3/589504794/WW/LZ/ZZ/134163192/x6-retro-pandora-box-controllers-arcade-video-game-machine.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/12/477599405/OU/CD/IP/88191712/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"The buyer is requesting the price of the engine part for the machine.","Country of Origin":"India","Game Name":"Catch the Baton","Operation Mode":"Coin Operated"}</t>
+          <t>{"Dimensions":"360","Quantity":"1","Quantity Unit":"Unit(s)"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>149784220063</t>
+          <t>149813842875</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HIMANI Fast Relief Ayurvedic Pain Relief Ointment</t>
+          <t>Tanki Anaz Ki.....</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ayurvedic Pain Relief Ointment</t>
+          <t>Grain Silo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"Packaging Size":"30gm","Quantity":"10","Quantity Unit":"Tube"}</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>{"Buying Option":"Purchase","Material":"Mild Steel","Quantity":"5","Quantity Unit":"Piece","Storage Capacity(T)":"50 ton"}</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>isq_filled_title_mismatch, isq_filled_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.95).</t>
+          <t>Quantity 5 pieces contradicts silo description.</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.95</v>
+        <v>0.39</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>22662517933</t>
+          <t>2850952217130</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>HIMANI FAST RELIEF AYURVEDIC PAIN RELIEF OINTMENT</t>
+          <t>Tanki Anaz ki.....</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2020/9/EU/CB/PI/66984761/himani-fast-relief-ayurvedic-pain-relief-ointment.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/4/303295812/CV/VQ/HZ/102731798/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"Packaging Size":"30gm","Quantity":"10","Quantity Unit":"Tube"}</t>
+          <t>{"Buying Option":"Purchase","Material":"Mild Steel","Quantity":"5","Quantity Unit":"Piece","Storage Capacity(T)":"50 ton"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>149745838985</t>
+          <t>149856912267</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phenelzine 15mg, Tablets</t>
+          <t>Tycoon Bag</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Antidepressant &amp; Anti Anxiety Medicines</t>
+          <t>Backpacks</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Box"}</t>
+          <t>{"Bag Type":"Fancy","Buyer Filled Details":"Matty, Embroidery","Customization":"No Print","Material":"Canvas","Quantity":"2","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2327,754 +2295,734 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.52). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>Title 'Tycoon Bag' not specific to backpacks category.</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2859639821033</t>
+          <t>2850361310097</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Phenelzine 15mg, Tablets</t>
+          <t>Tycoon Bag</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/8/630890641/ZH/AY/RP/272519476/screenshot-2026-07-30-at-12-28-29-pm.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/2/OK/WF/NR/51839993/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Box"}</t>
+          <t>{"Bag Type":"Fancy","Buyer Filled Details":"Matty, Embroidery","Customization":"No Print","Material":"Canvas","Quantity":"2","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>149747407463</t>
+          <t>149845698546</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ferlikiss 10 5 39 Plus Te Fertilizer</t>
+          <t>Gulf Lubricants</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NPK Fertilizer</t>
+          <t>Gulf Lubricating Oil</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Liquid","NPK Ratio":"19:19:19","Packaging Size":"10 kg","Physical Form":"Powder","Quantity":"5","Quantity Unit":"Litre"}</t>
+          <t>{"Product Category":"Engine Oil","Quantity":"210","Quantity Unit":"Litre","Viscosity Grade":"46"}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.78).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.74).</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2857736048630</t>
+          <t>2854363689733</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ferlikiss 10 5 39 Plus TE Fertilizer</t>
+          <t>Gulf Engine Oil</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/10/553895877/CQ/QN/QI/80405924/ferlikiss-10-5-39-te.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/5/514547418/CY/ZE/OE/60762069/gulf-engine-oil.jpg</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Liquid","NPK Ratio":"19:19:19","Packaging Size":"10 kg","Physical Form":"Powder","Quantity":"5","Quantity Unit":"Litre"}</t>
+          <t>{"Product Category":"Engine Oil","Quantity":"210","Quantity Unit":"Litre","Viscosity Grade":"46"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>149767023067</t>
+          <t>149858986195</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zaher Co Homeopathic Drugs Dilution 200 ml</t>
+          <t>Dairy Milk Heart Chocolate</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Homeopathic Drugs</t>
+          <t>Cadbury Dairy Milk Chocolate</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"Dosage Form":"Dilution","Packaging Size":"200 ml","Quantity":"1","Quantity Unit":"Bottle"}</t>
+          <t>{"MRP":"Rs 100","Net Weight":"150 g","Quantity":"2","Quantity Unit":"Piece","Sub-Brand":"Roast Almond"}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.73).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.83).</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19785420097</t>
+          <t>2857433301188</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Zaher-Co</t>
+          <t>Dairy Milk Heart Chocolate</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/LK/YR/MY-25553800/zaher-co.png</t>
+          <t>http://5.imimg.com/data5/WA_9696/Default/2025/8/540623893/GV/ZO/MB/139089603/image.jpeg</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"Dosage Form":"Dilution","Packaging Size":"200 ml","Quantity":"1","Quantity Unit":"Bottle"}</t>
+          <t>{"MRP":"Rs 100","Net Weight":"150 g","Quantity":"2","Quantity Unit":"Piece","Sub-Brand":"Roast Almond"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>149800762446</t>
+          <t>149855685934</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Velvet fangiside Plant Growth Regulator</t>
+          <t>Appalto Load Cells Transducer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paclobutrazol</t>
+          <t>Keli Load Cells</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Kitne ki padegi1 Litar","Quantity":"1","Quantity Unit":"Litre","Technical Name":"Paclobutrazol"}</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Brand":"Keli","Buyer Filled Details":"Sensocar","Capacity":"30 ton","Load Cell Type":"Ball and Cup","Quantity":"4","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.14). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.74).</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.14</v>
+        <v>0.74</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23745657848</t>
+          <t>21928580988</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Velvet Synthesiser Plant Growth Regulator</t>
+          <t>Appalto Load Cells Transducer</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2021/7/LA/MN/CR/134554010/ajinkya-s-velvet-jpg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/9/346531936/XV/TA/AW/36555467/appalto-load-cells-transducer.jpg</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Kitne ki padegi1 Litar","Quantity":"1","Quantity Unit":"Litre","Technical Name":"Paclobutrazol"}</t>
+          <t>{"Brand":"Keli","Buyer Filled Details":"Sensocar","Capacity":"30 ton","Load Cell Type":"Ball and Cup","Quantity":"4","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>149744279552</t>
+          <t>149867316134</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Aluminium Glass Pillar</t>
+          <t>Patanjali Pradarsudha Syrup</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Decorative Glass Pillar</t>
+          <t>Ayurvedic Health Tonic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>{"Design":"Plain","Height":"8 feet","Quantity":"200","Quantity Unit":"Piece","Shape":"Round"}</t>
+          <t>{"Flavor Profile":"Classic Mint-Lime","Packaging Type":"Glass Bottle","Quantity":"4","Quantity Unit":"Bottle","Type of Requirement":"Weekly","Volume":"500 ml"}</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>23764940862</t>
+          <t>20184671791</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Aluminium Glass Pillar</t>
+          <t>Patanjali Pradarsudha Syrup</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2021/7/IU/WC/TX/65446226/new-product.jpg</t>
+          <t>http://4.imimg.com/data4/GX/GI/GY/NSDMERP-67193617/67193617product11538991487.jpg</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"Design":"Plain","Height":"8 feet","Quantity":"200","Quantity Unit":"Piece","Shape":"Round"}</t>
+          <t>{"Flavor Profile":"Classic Mint-Lime","Packaging Type":"Glass Bottle","Quantity":"4","Quantity Unit":"Bottle","Type of Requirement":"Weekly","Volume":"500 ml"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>149766596113</t>
+          <t>149834222052</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stainless Steel Scrapbook Paper Display Rack, 15 Shelves</t>
+          <t>Navratri Kalash Stand</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Book Display Rack</t>
+          <t>Traditional Kalash</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"Design":"Double Sided","Load per Shelf":"40-50 kg","Material":"Stainless Steel","Quantity":"2","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"8 inch","Capacity":"5 Litre","Height":"6 inch","Material":"German Silver","Quantity":"100","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>21337220388</t>
+          <t>2857494053388</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Scrapbook Paper Display Rack</t>
+          <t>Navratri Kalash Stand</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2021/1/UW/JF/AA/91629529/scrapbook-paper-display-rack.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2026/7/623519345/CV/GN/WA/73879007/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"Design":"Double Sided","Load per Shelf":"40-50 kg","Material":"Stainless Steel","Quantity":"2","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"8 inch","Capacity":"5 Litre","Height":"6 inch","Material":"German Silver","Quantity":"100","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>149804589985</t>
+          <t>149863010285</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Apollo Engraving Machine</t>
+          <t>Rajwadi Moli</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CNC Engraving Machine</t>
+          <t>Pooja Kalawa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"Application":"Industrial","Material":"Metal","Working Area":"2x2 ft"}</t>
+          <t>{"Color":"Red","Quantity":"2","Quantity Unit":"Kg","Shape":"Reel"}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.67).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.72).</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2856764922597</t>
+          <t>2855672327648</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Apollo Engraving Machine</t>
+          <t>Rajwadi Moli</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/6/520329337/GY/BR/XT/48590926/product-jpeg.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/1/483150971/JE/GS/IB/208083620/prod-20250123-1416044942184887024975789-jpg.jpg</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"Application":"Industrial","Material":"Metal","Working Area":"2x2 ft"}</t>
+          <t>{"Color":"Red","Quantity":"2","Quantity Unit":"Kg","Shape":"Reel"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>149749704452</t>
+          <t>149810762285</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2 HP Kissan Shakti Electric Motor</t>
+          <t>Embroidery Machine Thread Break Sensor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Single Phase Electric Motor</t>
+          <t>Yarn Sensor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"Power":"2 HP"}</t>
+          <t>{"Quantity":"10","Quantity Unit":"piece","Type":"Electronic"}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.71).</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2850027883291</t>
+          <t>2848959033812</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2 hp Kissan Shakti electric motor</t>
+          <t>Embroidery Machine Thread Break Sensor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/1/UH/PP/QE/15328968/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/11/PG/OS/TT/6387069/embroidery-machine-thread-break-sensor.jpg</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"Power":"2 HP"}</t>
+          <t>{"Quantity":"10","Quantity Unit":"piece","Type":"Electronic"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>149742555813</t>
+          <t>149862393685</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Original Nariyal Pani</t>
+          <t>Tent House Stage Chowki</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Coconut Water</t>
+          <t>Tent House</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Tetra Pack, Bottle","Packaging Type":"Loose"}</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Size":"12x24 ft"}</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.17). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.17</v>
+        <v>0.85</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2856424340048</t>
+          <t>22738531648</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Original Nariyal Pani</t>
+          <t>Tent House Stage Chowki</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/4/505907452/CL/MV/SS/16061953/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/IOS/Default/2022/9/MU/YH/WX/29415522/product-jpeg.png</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Tetra Pack, Bottle","Packaging Type":"Loose"}</t>
+          <t>{"Size":"12x24 ft"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>149770276146</t>
+          <t>149868593475</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RJ-45/CAT6 Connector Crimping Machine</t>
+          <t>Car Headlight Lens Fortuner</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Crimping Machine</t>
+          <t>Car Headlight</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{"Capacity(T)":"1 Ton"}</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.54). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2853018259812</t>
+          <t>2852929955362</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>RJ-45/CAT6 CONNECTOR CRIMPING MACHINE</t>
+          <t>Car Headlight Lens fortuner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/12/366720664/WO/II/HQ/40679934/screenshot-2023-12-08-144457.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/11/363588527/QY/NT/IH/113442506/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"Capacity(T)":"1 Ton"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>149742405546</t>
+          <t>149815866352</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Racold Heat Pump Domestic Water Heater</t>
+          <t>Gandhak Potash Powder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Heat Pumps</t>
+          <t>Potash Feldspar Powder</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>{"Application":"Residential","Capacity":"200 L","Finance/Loan Requirement":"No","Power":"2 kW"}</t>
+          <t>{"Packaging Size":"25 kg","Quantity":"2","Quantity Unit":"Kg","Why do you need this":"For Business Use"}</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.83).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.72).</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25457963733</t>
+          <t>2855227883991</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Racold Heat Pump Domestic Water Heater</t>
+          <t>Gandhak Potash Powder</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/4/GS/LS/ME/101020172/racold-heat-pump-domestic-water-heater.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/10/549976391/QS/JW/XU/20780706/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"Application":"Residential","Capacity":"200 L","Finance/Loan Requirement":"No","Power":"2 kW"}</t>
+          <t>{"Packaging Size":"25 kg","Quantity":"2","Quantity Unit":"Kg","Why do you need this":"For Business Use"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>149764986763</t>
+          <t>149811699846</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Samsung Interactive Display Samsung Wa75f</t>
+          <t>Marlboro LED Ambient Lamp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Samsung LED Displays</t>
+          <t>LED Floor Lamp</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>{"Operating System":"Android 14","Product Type":"Interactive Panel","Screen Size":"75 inch"}</t>
+          <t>{"Buyer Filled Details":"40 W, 60 W, 75 W, 100 W, 150 W","Power":"25 W"}</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.7).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.77).</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2854272770773</t>
+          <t>2859024356462</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Samsung Interactive Display Samsung WA75F</t>
+          <t>Marlboro LED Ambient Lamp</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/4/504171989/KK/OJ/LH/96552438/samsung-interactive-display-samsung-wa75f.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2026/3/595466182/YF/UZ/JF/10417170/rl.png</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"Operating System":"Android 14","Product Type":"Interactive Panel","Screen Size":"75 inch"}</t>
+          <t>{"Buyer Filled Details":"40 W, 60 W, 75 W, 100 W, 150 W","Power":"25 W"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>149800974195</t>
+          <t>149808119746</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10Kg Composite Cylinder</t>
+          <t>E Rikshaw Charger Second Hand</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Composite Cylinder</t>
+          <t>E-Rickshaw Battery Charger</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>{"Application":"Domestic","Capacity (Kg)":"10 kg","Features":"Lightweight"}</t>
+          <t>{"Brand":"UTL","Output Current":"16 A","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.86).</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.86</v>
+        <v>0.48</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2851974348130</t>
+          <t>27376394548</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10Kg Composite Cylinder</t>
+          <t>E RIKSHAW charger second hand</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/8/333657676/MR/XT/ZJ/113540758/product-jpeg.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2022/10/CV/SC/QT/162631886/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"Application":"Domestic","Capacity (Kg)":"10 kg","Features":"Lightweight"}</t>
+          <t>{"Brand":"UTL","Output Current":"16 A","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>149794955259</t>
+          <t>149872585375</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USED Yamaha Jet Ski for Sale</t>
+          <t>Adjustable Motor Bed</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jet Ski</t>
+          <t>Adjustable Beds</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>{"Material":"Fiberglass"}</t>
+          <t>{"Bed Type":"Plain Bed","Number of Functions":"1 Function","Operation Mode":"Manual"}</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3088,1218 +3036,1190 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2853399031548</t>
+          <t>2855665481712</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>USED YAMAHA JET SKI FOR SALE</t>
+          <t>Adjustable Motor Bed</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/2/385151112/HY/SP/SX/193856518/used-yamaha-jet-ski-for-sale.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/1/482812658/AS/FV/BV/13070199/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"Material":"Fiberglass"}</t>
+          <t>{"Bed Type":"Plain Bed","Number of Functions":"1 Function","Operation Mode":"Manual"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>149792866013</t>
+          <t>149812206163</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Agriculture Battery Sprayer Pump Body</t>
+          <t>Unwanted Kit Tablet</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Agricultural Sprayer Component</t>
+          <t>Mifepristone Misoprostol Tablet</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>{"Component Type":"Nozzle","Material":"Plastic","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Farming Use","Used For Sprayer":"Power Sprayer"}</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>{"I want this for":"Pharma Third party manufacturing"}</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.72).</t>
+          <t>Title and mcat describe different products.</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2850439790730</t>
+          <t>2853984128312</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Agriculture Battery Sprayer Pump Body</t>
+          <t>Unwanted Kit Tablet</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/3/ZI/FH/RP/134688330/20-l-body.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/414519846/ZQ/ZD/TA/220436505/kmyv2or9oq03aga2qarc.jpg</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"Component Type":"Nozzle","Material":"Plastic","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Farming Use","Used For Sprayer":"Power Sprayer"}</t>
+          <t>{"I want this for":"Pharma Third party manufacturing"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>149742709495</t>
+          <t>149852239113</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Honda Cb Unicorn 160 Body Part</t>
+          <t>8 inch Green Banana Leaf Design Paper Bowl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Honda Bike Spare Parts</t>
+          <t>Paper Bowls</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>{"Color":"Black","Part Name":"Body Parts","Quantity":"1","Quantity Unit":"Piece","Vehicle Model":"Honda cb unicorn 160"}</t>
+          <t>{"GSM":"120 GSM","Material":"Silver Foil Paper","Quantity":"50","Quantity Unit":"Piece","Size":"8 inch","Usage/Application":"Food Service"}</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.61).</t>
+          <t>No mismatches detected.</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2857305100088</t>
+          <t>2851261187233</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Honda Cb Unicorn 160 Body Part</t>
+          <t>6inch Green Banana Leaf Design Paper Bowl</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/8/537925755/US/WI/RY/163759741/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/5/309938272/NP/OL/YV/26696261/6inch-printed-paper-bowl-500x500.jpg</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"Color":"Black","Part Name":"Body Parts","Quantity":"1","Quantity Unit":"Piece","Vehicle Model":"Honda cb unicorn 160"}</t>
+          <t>{"GSM":"120 GSM","Material":"Silver Foil Paper","Quantity":"50","Quantity Unit":"Piece","Size":"8 inch","Usage/Application":"Food Service"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>149747968313</t>
+          <t>149834906163</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sabotage 002 Matte Lipstick</t>
+          <t>JAI Kissan Digital Universal Mpu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Matte Lipstick</t>
+          <t>Motor Automatic Switch</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"Brand":"Colourbar","Product Form":"Crayon","Quantity":"2","Quantity Unit":"Piece","Set Size":"4 pieces"}</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>{"Buyer Filled Details":"Three Phase"}</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.9).</t>
+          <t>Title and mcat describe different products.</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25232454373</t>
+          <t>2854210070391</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Colorbar Sabotage 002 matte lipstick</t>
+          <t>JAI KISSAN DIGITAL UNIVERSAL MPU</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/3/QG/IT/FY/149387802/colorbar-sabotage-matte-lipstick.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/6/424592909/CO/DM/PH/99031334/jai-kissan-digital-universal-mpu.jpeg</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"Brand":"Colourbar","Product Form":"Crayon","Quantity":"2","Quantity Unit":"Piece","Set Size":"4 pieces"}</t>
+          <t>{"Buyer Filled Details":"Three Phase"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>149790148159</t>
+          <t>149847116867</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>28mm Bisleri Green Water Bottle Cap Alaska Neck</t>
+          <t>24 Inch Unitech LED TV Combo Card</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Water Bottle Cap</t>
+          <t>LED TV Motherboard</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>{"Bottle Capacity":"1 L","Buyer Filled Details":"500 ml, And we plan for customized logo","Quantity":"50000","Quantity Unit":"Piece"}</t>
+          <t>{"Device Type":"LED","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2853104218848</t>
+          <t>23306866912</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>28mm Bisleri Green Water Bottle Cap Alaska Neck</t>
+          <t>24 Inch Unitech LED TV Combo Card</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/12/367559869/GC/II/PZ/187351419/pp-water-bottle-cap-28mm-alaska-neck-bisleri-green-colour.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/4/TU/GI/DA/23100183/24-inch-led-tv-card-combo.png</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"Bottle Capacity":"1 L","Buyer Filled Details":"500 ml, And we plan for customized logo","Quantity":"50000","Quantity Unit":"Piece"}</t>
+          <t>{"Device Type":"LED","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>149760858763</t>
+          <t>149859985646</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Super Splendor Bike Body Parts Black</t>
+          <t>DC 6v 380ma 500mmhg Micro Air Pump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hero Bike Body Kit</t>
+          <t>Air Pumps</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>{"Bike Model":"Splendor","Color":"Black","Model Variant":"New Model","Quantity":"1","Quantity Unit":"Set","Usage/Application":"Workshop Use"}</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Quantity":"10","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.56). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2852698029630</t>
+          <t>26563245330</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Super Splendor Bike Body Parts Black</t>
+          <t>DC 6V 380mA 500mmHg Micro Air Pump</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/10/353740537/HG/UO/AU/196210963/super-splendor-body-parts.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/9/MZ/ZY/AT/99344521/dc-air-pump-motor.jpg</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"Bike Model":"Splendor","Color":"Black","Model Variant":"New Model","Quantity":"1","Quantity Unit":"Set","Usage/Application":"Workshop Use"}</t>
+          <t>{"Quantity":"10","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>149802364095</t>
+          <t>149823848667</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>32 Inch MI TV Display Panel</t>
+          <t>Carissa Carandas(kalaka)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MI LED TV</t>
+          <t>Karonda Pickle</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>{"Flavor":"Sour","Preparation Style":"Whole","Quantity":"1","Quantity Unit":"kg"}</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch, isq_filled_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.63).</t>
+          <t>Title is raw fruit, mcat is pickle; preparation style irrelevant.</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2854051074273</t>
+          <t>22529870148</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>32 Inch MI TV Display Panel</t>
+          <t>Carissa Carandas(Kalaka)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2024/5/417812434/DP/II/AY/101686493/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2020/8/UH/IL/YK/52597500/prod-20200816-1329278565191186279365806-jpg.jpg</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Flavor":"Sour","Preparation Style":"Whole","Quantity":"1","Quantity Unit":"kg"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>149737117695</t>
+          <t>149862823863</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E Mail Sending Work</t>
+          <t>HEXAFEED 1 Powder</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Email Marketing</t>
+          <t>Baby Milk Powder</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Grade Standard":"USP","I want this for":"Reselling","Quantity":"5","Quantity Unit":"Kg"}</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.61).</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8716163355</t>
+          <t>2852468868662</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>E Mail Sending Work</t>
+          <t>HEXAFEED 1 POWDER</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>http://3.imimg.com/data3/RO/AG/MY-13917182/images-thumbs-1.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/5/514748065/SC/LJ/AR/41111817/hexafeed-1-powder.jpg</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Grade Standard":"USP","I want this for":"Reselling","Quantity":"5","Quantity Unit":"Kg"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>149801028134</t>
+          <t>149859130575</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birthday Currency Note</t>
+          <t>Chlorpyrifos 1 Litre 20% TC Termite</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dummy Currency Notes</t>
+          <t>Chlorpyrifos</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>{"Denomination":"200","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Brand":"Lethal TC","Chlorpyrifos Concentration":"20 %","Formulation Type":"TC (Termite)","Packaging Size":"1 Litre","Quantity":"1","Quantity Unit":"Litre"}</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.7).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25545458791</t>
+          <t>24214251612</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Birthday Currency Note</t>
+          <t>500 ml. IIL Lethal TC (Chlorpyrifos 20 % EC) Insecticide</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/4/HP/OF/DH/22934633/birthday-currency-note.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/11/FS/OL/TR/5532647/indiamart.jpeg</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"Denomination":"200","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Brand":"Lethal TC","Chlorpyrifos Concentration":"20 %","Formulation Type":"TC (Termite)","Packaging Size":"1 Litre","Quantity":"1","Quantity Unit":"Litre"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>149795728952</t>
+          <t>149855589375</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tushi Plus Cream</t>
+          <t>JAICOBA Q10 Capsule</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ayurvedic Skin Creams</t>
+          <t>Coenzyme Q10 Tablets and Capsules</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>{"I want this for":"Personal Use","Packaging Size":"30 gm","Quantity":"2","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Dosage Form":"Capsule","Quantity":"5","Quantity Unit":"Strip"}</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.54). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.68).</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25159027991</t>
+          <t>21901331330</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Tushi Plus Cream</t>
+          <t>JAICOBA Q10 TABLET</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/7/528463072/DC/UO/QG/39532339/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/12/471800540/AG/KW/JO/41252628/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"I want this for":"Personal Use","Packaging Size":"30 gm","Quantity":"2","Quantity Unit":"Piece"}</t>
+          <t>{"Dosage Form":"Capsule","Quantity":"5","Quantity Unit":"Strip"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>149787782263</t>
+          <t>149866081834</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SS Joint Cap Fitting 270 (pvc End Cap )</t>
+          <t>LED Display Repairing Service</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PVC End Cap</t>
+          <t>LED TV Repairing Services</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"Quantity":"200","Quantity Unit":"piece","Shape":"Square","Size":"4 inch","Type":"Threaded"}</t>
+          <t>{"Problem Type":"Display Issue","Screen Size":"32 inch","TV Brand":"TCL"}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.64).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>23091925348</t>
+          <t>2849951773630</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SS Joint Cap fitting 270 (pvc end cap )</t>
+          <t>Led Tv Display Panel</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2022/5/CW/AX/ZS/79813730/1653106203187-jpg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/1/MP/YL/VJ/55430138/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"Quantity":"200","Quantity Unit":"piece","Shape":"Square","Size":"4 inch","Type":"Threaded"}</t>
+          <t>{"Problem Type":"Display Issue","Screen Size":"32 inch","TV Brand":"TCL"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>149750274285</t>
+          <t>149828485452</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vansal Almonard Farrata Fan Extra Heavy Duty</t>
+          <t>200 Ltr PU Thinner</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Almonard Pedestal Fan</t>
+          <t>Polyurethane Thinner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>{"Brand":"Almonard","Fan Type":"Farata","Quantity":"1","Quantity Unit":"Piece","Sweep Size":"24 inch (600 mm)"}</t>
+          <t>{"Drying Speed":"Fast Drying","Packaging Size":"200 L","Quantity":"200","Quantity Unit":"Litre","Thinner Grade":"2K PU Grade"}</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.6).</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19435967548</t>
+          <t>27461458833</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Vansal Vayu Farrata Fan Extra Heavy Duty</t>
+          <t>200 Ltr Pu Thinner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/PC/KE/ANDROID-52018551/product.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2022/11/NV/NS/EI/59533232/200-ltr-pu-thinner.webp</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"Brand":"Almonard","Fan Type":"Farata","Quantity":"1","Quantity Unit":"Piece","Sweep Size":"24 inch (600 mm)"}</t>
+          <t>{"Drying Speed":"Fast Drying","Packaging Size":"200 L","Quantity":"200","Quantity Unit":"Litre","Thinner Grade":"2K PU Grade"}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>149747210375</t>
+          <t>149860613834</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PVC Syringe Scrap</t>
+          <t>8 Bottle Fantom Goli Soda Set</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Plastic Scrap</t>
+          <t>Goli Soda Glass Bottle</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>{"Color":"Natural","Form":"Bale","Material":"PVC","Quantity":"1000","Quantity Unit":"Kg","Usage/Application":"Manufacturing"}</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Capacity":"200 ml","Material":"Glass","Quantity":"40","Quantity Unit":"Piece","Weight":"560 g"}</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.56). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.84).</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2856123885148</t>
+          <t>2852415744573</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Plastic Syringe Scrap</t>
+          <t>8 Bottle Fantom Goli Soda Set</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/3/496143694/UP/AL/PO/144095355/plastic-syringes.jpeg</t>
+          <t>http://5.imimg.com/data5/WA_9696/Default/2026/2/584728253/GR/GK/TE/198043502/image.jpeg</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"Color":"Natural","Form":"Bale","Material":"PVC","Quantity":"1000","Quantity Unit":"Kg","Usage/Application":"Manufacturing"}</t>
+          <t>{"Capacity":"200 ml","Material":"Glass","Quantity":"40","Quantity Unit":"Piece","Weight":"560 g"}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>149794987863</t>
+          <t>149847203413</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Blue Candle Wax - Multi Colours</t>
+          <t>Orapass Gel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Candle Color</t>
+          <t>Choline Salicylate and Lignocaine Hydrochloride Gel</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>{"Color":"Blue","Form":"Powder","Packaging Size":"5 Liter","Quantity":"10","Quantity Unit":"Kg"}</t>
+          <t>{"I want this for":"Reselling","Packaging Size":"10 Gram"}</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
+          <t>No mismatches detected.</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2858913244855</t>
+          <t>2854892029673</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Pearl Candle Wax - Multi colours</t>
+          <t>Orapass gel</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/3/589081680/CI/SG/ZK/31365937/prarl-wax-colours.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/2/490070295/OV/OI/TN/53126631/product-jpeg.jpeg</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"Color":"Blue","Form":"Powder","Packaging Size":"5 Liter","Quantity":"10","Quantity Unit":"Kg"}</t>
+          <t>{"I want this for":"Reselling","Packaging Size":"10 Gram"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>149750772134</t>
+          <t>149809929813</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charminar Cement Sheets 10 Feet</t>
+          <t>Men Red Varsity Jacket</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Charminar Cement Sheets</t>
+          <t>Varsity Jackets</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"4 ft","Length":"10 ft","Quantity":"108","Quantity Unit":"Piece","Thickness":"6 mm"}</t>
+          <t>{"Fabric Weight":"350 GSM","Material":"Cotton","Quantity":"1","Quantity Unit":"Piece","Sleeve Material":"Polyester"}</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.78).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.69).</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2852908367497</t>
+          <t>23456808791</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Charminar Cement Sheets 10 Feet</t>
+          <t>Men Red  Varsity Jacket</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/11/362649907/HG/QQ/CN/119728438/charminar-cement-sheets.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/5/QJ/UP/WC/24106032/varsity-jacket.jpg</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"4 ft","Length":"10 ft","Quantity":"108","Quantity Unit":"Piece","Thickness":"6 mm"}</t>
+          <t>{"Fabric Weight":"350 GSM","Material":"Cotton","Quantity":"1","Quantity Unit":"Piece","Sleeve Material":"Polyester"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>149794849813</t>
+          <t>149812033085</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lenzing Micromodal Fabric</t>
+          <t>Calculator Pencil Box</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cotton Modal Fabric</t>
+          <t>Pencil Box</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>{"Fabric Type":"Micro Modal","Quantity":"1000","Quantity Unit":"meter","Usage/Application":"Undergarments","Weight":"160 GSM"}</t>
+          <t>{"Buyer Filled Details":"Medium, Wood","Material":"Plastic","Size":"Small"}</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.67).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.84).</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2856355863097</t>
+          <t>2858087728555</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Lenzing Micromodal Fabric</t>
+          <t>Calculator Pencil Box</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/5/509692888/SS/OH/GL/188560187/lenzing-micromodal-fabric.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/12/565411067/KP/YN/HO/18740448/calculator-pencil-box.png</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"Fabric Type":"Micro Modal","Quantity":"1000","Quantity Unit":"meter","Usage/Application":"Undergarments","Weight":"160 GSM"}</t>
+          <t>{"Buyer Filled Details":"Medium, Wood","Material":"Plastic","Size":"Small"}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>149752905585</t>
+          <t>149845528146</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>U Gold- 26kg</t>
+          <t>Aluminum Whisk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HMT Rice</t>
+          <t>Aluminium Utensils</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Buyer needs 26 kg Lachakari Raw Rice, 12 months old, in a good bag.","Packaging Size":"26 kg","Processing Type":"Raw","Quality Grade":"Gold","Quantity":"1","Quantity Unit":"Bag"}</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Quantity":"1","Quantity Unit":"Piece","Size":"10 Inch","Type of Requirement":"Sample Only"}</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.23). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.82).</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.23</v>
+        <v>0.82</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2859048975133</t>
+          <t>2853345651633</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>U gold- 26kg</t>
+          <t>Aluminum Whisk</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2026/4/596908875/MH/BF/FE/112068928/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/2/382622066/LX/AO/HW/32662336/aluminium-18-inches-ladle.jpg</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Buyer needs 26 kg Lachakari Raw Rice, 12 months old, in a good bag.","Packaging Size":"26 kg","Processing Type":"Raw","Quality Grade":"Gold","Quantity":"1","Quantity Unit":"Bag"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece","Size":"10 Inch","Type of Requirement":"Sample Only"}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>149790551575</t>
+          <t>149841764963</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Diamond Masala Puff</t>
+          <t>300 GSM Cotton Canvas Tote Bags</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Corn Puff</t>
+          <t>Canvas Tote Bags</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>{"Flavor":"Masala","Processing State":"Roasted","Quantity":"30","Quantity Unit":"Pack","Shape":"Puff"}</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Color":"Off-white","Dimensions":"14 x 16 inch","Fabric Weight":"300 GSM","Quantity":"5","Quantity Unit":"piece","Usage/Application":"Resale"}</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.44). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2853884032488</t>
+          <t>2853951271888</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Diamond Pudina Puff</t>
+          <t>300 GSM Cotton Canvas Tote Bags</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/409842701/VW/EO/JK/205370175/diamond-pudina-puff.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/412979793/DL/IJ/FE/118482489/whatsapp-image-2024-04-24-at-9-51-26-am.jpeg</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"Flavor":"Masala","Processing State":"Roasted","Quantity":"30","Quantity Unit":"Pack","Shape":"Puff"}</t>
+          <t>{"Color":"Off-white","Dimensions":"14 x 16 inch","Fabric Weight":"300 GSM","Quantity":"5","Quantity Unit":"piece","Usage/Application":"Resale"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>149792625634</t>
+          <t>149813485867</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wall Master - Noora Brush</t>
+          <t>Kaffir Lime Tree</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paint Brush</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.58). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Buyer Filled Details":"Grafted","Height":"2-2.5 ft","Plant Type":"Hybrid","Quantity":"10","Quantity Unit":"Plant"}</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>0.58</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>11080041497</t>
+          <t>2854733166030</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Wall Master - Noora Brush</t>
+          <t>Kaffir Lime Tree</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/LU/VD/MY-891889/img_0460snk.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/8/445782589/HW/GD/LP/33712158/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Buyer Filled Details":"Grafted","Height":"2-2.5 ft","Plant Type":"Hybrid","Quantity":"10","Quantity Unit":"Plant"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>149744370313</t>
+          <t>149828135663</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Honda Cb Unicorn 160 Body Part</t>
+          <t>Fire Crackers</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Honda Bike Spare Parts</t>
+          <t>Colorful Cracker</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Honda CB unicorn 160, Visor kit all","Color":"Black","Part Name":"Body Parts","Quantity":"1","Quantity Unit":"Set","Vehicle Model":"Price"}</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>{"Origin":"Sivakasi","Packaging Quantity":"10 Pcs/Box","Quantity":"5","Quantity Unit":"Box","Usage/Application":"Distribution"}</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.61).</t>
+          <t>Title and mcat describe different product categories.</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2857305100088</t>
+          <t>26475289888</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Honda Cb Unicorn 160 Body Part</t>
+          <t>Nazi Green Bomb</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/8/537925755/US/WI/RY/163759741/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2022/8/LJ/KJ/MV/6398711/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Honda CB unicorn 160, Visor kit all","Color":"Black","Part Name":"Body Parts","Quantity":"1","Quantity Unit":"Set","Vehicle Model":"Price"}</t>
+          <t>{"Origin":"Sivakasi","Packaging Quantity":"10 Pcs/Box","Quantity":"5","Quantity Unit":"Box","Usage/Application":"Distribution"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>149796988785</t>
+          <t>149860653846</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FELFIL Filament Maker</t>
+          <t>Egg Free Cake Rusk Concentrate Mix</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3D Printer</t>
+          <t>Eggless Cake Premix</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"Brand":"Bambu Lab","Build Volume":"220x220x250 mm","Material Type":"PLA"}</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Flavor":"Vanilla","Quantity":"2","Quantity Unit":"Kg"}</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.44). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.74).</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>23049737973</t>
+          <t>2852587724730</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>FELFIL Filament Maker</t>
+          <t>Egg Free Cake Rusk Concentrate Mix</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2021/1/KP/UO/IP/71683659/felfil-filament-maker.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/10/349195328/LA/FR/JZ/95993366/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"Brand":"Bambu Lab","Build Volume":"220x220x250 mm","Material Type":"PLA"}</t>
+          <t>{"Flavor":"Vanilla","Quantity":"2","Quantity Unit":"Kg"}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>149794012995</t>
+          <t>149816118752</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rear No Plate for Royal Enfield Uc Model</t>
+          <t>Ganesh Matka</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Royal Enfield Bike Spare Parts</t>
+          <t>Clay Cooking Pot</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4309,1807 +4229,1755 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.51). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>Title describes decorative Ganesh pot, mcat is cooking pot category.</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12357748573</t>
+          <t>2853448142197</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Rear No Plate for Royal Enfield UC Model</t>
+          <t>Ganesh matka</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/VM/RD/MY-7664924/rear-no-plate-for-royal-enfield-uc-model.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/5/415948503/XA/EG/ZU/213264901/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>149751352734</t>
+          <t>149749081295</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dayal Mono Zinc Sulphate 1,3,5kg</t>
+          <t>Indoor Badminton Courts Shed</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Zinc Sulphate</t>
+          <t>Badminton Court Roofing Shed</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"Quantity":"100","Quantity Unit":"Kg","Type":"Monohydrate","Zinc (Zn) Content":"33%"}</t>
+          <t>{"Quantity":"2500","Quantity Unit":"sq ft","Roofing Material":"Color Coated Sheet","Structure Type":"Truss"}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.82).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2854570822212</t>
+          <t>25946097297</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Dayal Mono Zinc Sulphate 1,3,5kg</t>
+          <t>Indoor Badminton Courts Shed</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/7/527083357/ZD/PP/QH/226612965/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2020/9/OK/OF/DE/75185696/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"Quantity":"100","Quantity Unit":"Kg","Type":"Monohydrate","Zinc (Zn) Content":"33%"}</t>
+          <t>{"Quantity":"2500","Quantity Unit":"sq ft","Roofing Material":"Color Coated Sheet","Structure Type":"Truss"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>149785355613</t>
+          <t>149806698163</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Foosball Table Balls</t>
+          <t>Sapphire Pulse Rx 6600 (pre-owned)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Foosball Table</t>
+          <t>Sapphire AMD Graphics Card</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"Frame Material":"MDF","Quantity":"1","Quantity Unit":"piece","Table Size":"4.5 ft (Standard)","Table Type":"Standing"}</t>
+          <t>{"Brand":"Sapphire","GPU Memory":"8 GB","GPU Model":"RX 580","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.89).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.89</v>
+        <v>0.66</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2850653011791</t>
+          <t>2856124825397</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Foosball Table Balls</t>
+          <t>Sapphire Pulse RX 6600 (Pre-Owned)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2023/4/297797628/UQ/BW/CP/24286651/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/3/496134813/KQ/PJ/IW/60763678/sapphire-pulse-rx-6600-pre-owned.png</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"Frame Material":"MDF","Quantity":"1","Quantity Unit":"piece","Table Size":"4.5 ft (Standard)","Table Type":"Standing"}</t>
+          <t>{"Brand":"Sapphire","GPU Memory":"8 GB","GPU Model":"RX 580","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>149806798659</t>
+          <t>149868877452</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nt71168mgg Gamma Chip LED TV</t>
+          <t>Samsung Galaxy S7 Edge Mobile Folder</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>IC Chip</t>
+          <t>Samsung Mobile Phones</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Novatek","Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.36). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.74).</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>21863252155</t>
+          <t>21780159355</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nt71168mgg Gamma  Chip  LED TV</t>
+          <t>Samsung Galaxy S7 Edge mobile Folder</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/PO/ZM/GY/SELLER-18701709/webp-net-resizeimage-13-.jpg</t>
+          <t>http://5.imimg.com/data5/AN/DN/YT/ANDROID-94918460/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Novatek","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>149746350275</t>
+          <t>149865793846</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cerium Misch Metal</t>
+          <t>Used Ahuja Ssa - 250m Mic Machine</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Rare Earth Metals</t>
+          <t>Ahuja Audio Amplifiers</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Kg"}</t>
+          <t>{"Power Output":"250 W"}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.63).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>18916655655</t>
+          <t>17199517712</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Cerium Misch Metal</t>
+          <t>Used AHUJA SSA - 250M Mic Machine</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/YJ/KT/MY-48282391/cerium-misch-metal.png</t>
+          <t>http://4.imimg.com/data4/ST/YU/ANDROID-49754413/product.jpeg</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Kg"}</t>
+          <t>{"Power Output":"250 W"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>149764911985</t>
+          <t>149865519046</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shade Card 1</t>
+          <t>Dhoop Stick Ceramic Stand</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paint Shade Card</t>
+          <t>Ceramic Incense Holder</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Quantity":"100","Quantity Unit":"Piece","Shape":"Katori Type","Usage Application":"Bambooless Holder"}</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0.8</v>
+        <v>0.51</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2851896483433</t>
+          <t>2856304829797</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Shade Card 1</t>
+          <t>Dhoop Stick Ceramic Stand</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/7/330357827/YL/FV/CY/22467963/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/4/499893367/IV/QU/QJ/57785004/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Quantity":"100","Quantity Unit":"Piece","Shape":"Katori Type","Usage Application":"Bambooless Holder"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>149774356313</t>
+          <t>149811208352</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hitachi Air Conditioner Spare Parts</t>
+          <t>Pregnenolone Steroid</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Air Conditioner Parts</t>
+          <t>Steroid</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>{"AC Type":"Ductable","Capacity":"5 Ton","Material":"Copper","Quantity":"1","Quantity Unit":"piece","Usage/Application":"Repair &amp; Service"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Bottle"}</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.67).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.88).</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>22182988491</t>
+          <t>2858711373397</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Hitachi Air Conditioner Spare Parts</t>
+          <t>Pregnenolone</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/YU/IL/QP/SELLER-37912570/rau518hwds-idu-jpg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2026/1/580127878/NU/LN/MW/5238588/product-jpeg.jpeg</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"AC Type":"Ductable","Capacity":"5 Ton","Material":"Copper","Quantity":"1","Quantity Unit":"piece","Usage/Application":"Repair &amp; Service"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Bottle"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>149792934852</t>
+          <t>149861415085</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mitsubishi Gs2107 HMI Repair</t>
+          <t>S &amp; B Shichimi Togarashi, 500 Gm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HMI Touch Panel</t>
+          <t>Masala Powder</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>{"Display Size":"7 inch","Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.36). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Buyer Filled Details":"Togrash","Packaging Size":"500 g","Packaging Type":"Packet","Quantity":"1","Quantity Unit":"Kg","Usage/Application":"Distribution"}</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>25983149930</t>
+          <t>22240668397</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Mitsubishi GS2107 HMI Touch Glass Repair</t>
+          <t>S &amp; B Shichimi Togarashi, 300 Gm</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/1/572526184/KS/TI/PS/141203390/mitsubishi-gs2107-hmi-touch-glass-repair.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/4/UT/BX/EL/8420590/s-b-shichimi-togarashi-300gm.jpg</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"Display Size":"7 inch","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"Togrash","Packaging Size":"500 g","Packaging Type":"Packet","Quantity":"1","Quantity Unit":"Kg","Usage/Application":"Distribution"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>149784223863</t>
+          <t>149834636595</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Herbal Hair Oil, 100 ml</t>
+          <t>Unwanted Kit</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Herbal Hair Oil</t>
+          <t>Mifepristone Misoprostol Tablet</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>{"Brand":"Neelambari","Key Benefits":"Hair Growth","Packaging Size":"100 ml","Quantity":"1","Quantity Unit":"Bottle"}</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>{"Composition":"Misoprostol","Packaging Size":"5 tablets","Packaging Type":"Combi-pack Kit","Quantity":"1","Quantity Unit":"Kit"}</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.9).</t>
+          <t>BI Layer Mismatch: Cosine similarity low (0.28). LLM fallback failed: HTTP Error 429: Too Many Requests</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.9</v>
+        <v>0.28</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2857756952691</t>
+          <t>2853373391930</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Herbal Hair Oil</t>
+          <t>Unwanted Kit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/10/555008454/NN/HV/PE/160306924/hair-oil.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/2/383699417/CE/FK/UY/144045951/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"Brand":"Neelambari","Key Benefits":"Hair Growth","Packaging Size":"100 ml","Quantity":"1","Quantity Unit":"Bottle"}</t>
+          <t>{"Composition":"Misoprostol","Packaging Size":"5 tablets","Packaging Type":"Combi-pack Kit","Quantity":"1","Quantity Unit":"Kit"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>149781473059</t>
+          <t>149806805695</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>- Pocket Meter</t>
+          <t>TVS Jupiter Bs6 Fuel Pump Motor</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Digital pH Meter</t>
+          <t>Fuel Pump Assembly</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"Quantity":"5","Quantity Unit":"piece","Usage/Application":"Resale"}</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Emission Standard":"BS6","Fuel Type":"Petrol","Quantity":"1","Quantity Unit":"piece","Vehicle Model":"2020"}</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.47). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.63).</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1962471962</t>
+          <t>27476518862</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>LAQUA Twin - Pocket Meter</t>
+          <t>TVS Jupiter Bs6 Fuel Pump Motor</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>http://4.imimg.com/data4/AV/RR/MY-2468618/conductivity.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2022/11/FX/XM/DO/18834648/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"Quantity":"5","Quantity Unit":"piece","Usage/Application":"Resale"}</t>
+          <t>{"Emission Standard":"BS6","Fuel Type":"Petrol","Quantity":"1","Quantity Unit":"piece","Vehicle Model":"2020"}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>149746287046</t>
+          <t>149864140085</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sound Gun</t>
+          <t>Party Welcome Girls and Girls Waiter</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Toy Gun</t>
+          <t>Girls Party Dresses</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>{"Material":"Metal","Quantity":"20","Quantity Unit":"Carton"}</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Fabric":"Net"}</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.59). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.63).</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2851925319473</t>
+          <t>25770703855</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Sound Cork Pistol</t>
+          <t>Party welcome girls and girls waiter</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/6/613322102/XX/SF/CS/138625925/sound-cork-pistol.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2022/5/YV/YL/TW/71898733/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"Material":"Metal","Quantity":"20","Quantity Unit":"Carton"}</t>
+          <t>{"Fabric":"Net"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>149776776813</t>
+          <t>149862290259</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Refurbished 16gb Ddr4 Laptop Ram</t>
+          <t>Metal Full Auto M92 - Blank Firing</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DDR4 RAM</t>
+          <t>Toy Gun</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>{"Capacity":"16 GB","Form Factor":"Laptop","Memory Speed":"2666 MHz","Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>{"Buyer Filled Details":"BB Gun, Manual","Material":"Metal","Operation Mode":"Manual","Product Type":"Airsoft Gun","Quantity":"1","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>isq_filled_title_mismatch</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
+          <t>OPERATION_MODE mismatch: title says Full Auto, filled says Manual.</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.8</v>
+        <v>0.34</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2853990026133</t>
+          <t>2855326651655</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Refurbished 16Gb Ddr4 Laptop Ram</t>
+          <t>Metal Full Auto M92 - Blank Firing</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/414814207/RV/FF/WK/62270066/16gb-ddr4-laptop-ram.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/11/467225042/RD/DW/SU/233738784/metal-full-auto-m92-blank-firing.jpg</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{"Capacity":"16 GB","Form Factor":"Laptop","Memory Speed":"2666 MHz","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"BB Gun, Manual","Material":"Metal","Operation Mode":"Manual","Product Type":"Airsoft Gun","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>149801118152</t>
+          <t>149817242067</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Organic Paneer Low Fat</t>
+          <t>Bathroom Cleaning Machine</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Organic Paneer</t>
+          <t>Cleaning Machinery</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"Certification":"FSSAI Certified","Milk Source":"Cow Milk","Packaging Size":"200 g","Paneer Type":"Pure Paneer","Quantity":"4","Quantity Unit":"Pack","Type of Requirement":"Weekly"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.68).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.77).</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2853307924962</t>
+          <t>2850320939230</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Organic Paneer Low Fat</t>
+          <t>Bathroom Cleaning Machine</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2024/1/380469725/XW/WG/AZ/65692023/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/10/455502261/GW/XV/GO/74786523/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"Certification":"FSSAI Certified","Milk Source":"Cow Milk","Packaging Size":"200 g","Paneer Type":"Pure Paneer","Quantity":"4","Quantity Unit":"Pack","Type of Requirement":"Weekly"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>149794731934</t>
+          <t>149867329495</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Apple iPhone 5s</t>
+          <t>Barbie-343 (ravi Hybrid Seeds) Indian Bean</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apple iPhone</t>
+          <t>Hybrid Bhindi Seeds</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Iphone 5s","Condition":"New","Internal Storage":"64 GB"}</t>
+          <t>{"Brand":"Ravi","Packaging Size":"500 g","Quantity":"1","Quantity Unit":"kg","Variety":"Barbie 343"}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.84).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.72).</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20173239130</t>
+          <t>2857201115197</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Apple Iphone 5s</t>
+          <t>Barbie-343 (Ravi Hybrid seeds) Indian bean</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/WX/RP/MY-10508560/iphone-5s-white.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/8/538903561/AZ/RD/FR/93087792/barbie-343-ravi-hybrid-seeds-indian-bean.jpeg</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Iphone 5s","Condition":"New","Internal Storage":"64 GB"}</t>
+          <t>{"Brand":"Ravi","Packaging Size":"500 g","Quantity":"1","Quantity Unit":"kg","Variety":"Barbie 343"}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>149763462475</t>
+          <t>149871332167</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Auto Refractometer</t>
+          <t>Yamaha R1m Kit for R15 V3 Custom Bodykit</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Used Refractometer</t>
+          <t>Yamaha Bike Body Kit</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"Brand":"Shin Nippon","Buyer Filled Details":"Justice Auto refractometer","Condition":"Second Hand","Finance/Loan Requirement":"No","Keratometer":"No Keratometer"}</t>
+          <t>{"Color":"Black","Compatible Bike Model":"R15 V3","Component Type":"Full Set","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.88).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.7).</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2851604957512</t>
+          <t>23824231197</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>TOPCON AR / RM 8800 (Used)</t>
+          <t>Yamaha R1m Kit For R15 V3 Custom Bodykit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/6/319094845/TL/ZN/QX/180818111/topcon-ar-rm-8800-used-.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2021/8/NB/EW/TG/90832463/2b9e6b4c-db11-4697-ba35-671cd2e27093.jpg</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"Brand":"Shin Nippon","Buyer Filled Details":"Justice Auto refractometer","Condition":"Second Hand","Finance/Loan Requirement":"No","Keratometer":"No Keratometer"}</t>
+          <t>{"Color":"Black","Compatible Bike Model":"R15 V3","Component Type":"Full Set","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>149796651146</t>
+          <t>149856617013</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Simpsons Hydraulic Oil Aw68</t>
+          <t>Dairy Farm Labour Supplier</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hydraulic Oils</t>
+          <t>Labour Contractors</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"ISO Viscosity Grade":"68","Quantity":"50","Quantity Unit":"litre"}</t>
+          <t>{"Industry":"Agricultural","Job Role":"General Labour","Skill Level":"Semi-skilled"}</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.82).</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25280471673</t>
+          <t>2852175563830</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Simpsons Hydraulic Oil Aw68</t>
+          <t>Dairy Farm Labour Supplier</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/3/DL/VF/YE/18512161/simpsons-hydraulic-oil-aw68.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/12/470342423/KA/UF/LY/195968651/dairy-farm-labour-supplier.jpg</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"ISO Viscosity Grade":"68","Quantity":"50","Quantity Unit":"litre"}</t>
+          <t>{"Industry":"Agricultural","Job Role":"General Labour","Skill Level":"Semi-skilled"}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>149751646075</t>
+          <t>149814363495</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GUCCI Brown White Canvas</t>
+          <t>Ola Electric Scooters Side Mirror</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Gucci Shoes</t>
+          <t>Scooty Side Mirrors</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"Quality Grade":"Premium","Shoe Type":"Formal","Upper Material":"Canvas"}</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.31). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.66).</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2856716092448</t>
+          <t>2855120058648</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>GUCC I BROWN WHITE</t>
+          <t>Ola Electric Scooters side mirror</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/6/517927218/IC/EB/KG/131860226/67766a2c3b5e7.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/10/555664541/MM/OU/ZP/13328757/ola-electric-scooters-side-mirror.webp</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"Quality Grade":"Premium","Shoe Type":"Formal","Upper Material":"Canvas"}</t>
+          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>149757186259</t>
+          <t>149807783285</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Printed Alpine Fabrics</t>
+          <t>VST Power Tiller Wheel Stud Bolts</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Alpine Fabric</t>
+          <t>Power Tiller Parts</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Compatible Brand":"VST Shakti","Fuel Type":"Diesel","Part Type":"Tines","Quantity":"2","Quantity Unit":"Piece"}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.88).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.67).</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2854646621648</t>
+          <t>2852650125273</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Printed Alpine Fabrics</t>
+          <t>VST Power Tiller Wheel Stud Bolts</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2024/8/442736774/UZ/FT/YS/144227352/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/10/353084277/TF/PT/HL/1122330/vst-power-tiller-wheel-stud-bolts.jpg</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Compatible Brand":"VST Shakti","Fuel Type":"Diesel","Part Type":"Tines","Quantity":"2","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>149767786813</t>
+          <t>149848906575</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rattan / Round Jula Wire</t>
+          <t>Pulsar Bike Front Mudguard</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cane Craft</t>
+          <t>Bajaj Bike Front Mudguard</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Bike Model":"Pulsar 150","Quantity":"1","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.13). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.13</v>
+        <v>0.85</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>23352860655</t>
+          <t>14691865888</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Rattan / Round Jula Wire</t>
+          <t>Pulsar Bike Front Mudguard</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2021/4/OK/HA/XH/8681279/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/DT/GT/MY-39491252/pulsar-bike-front-mudguard.jpg</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Bike Model":"Pulsar 150","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>149804390567</t>
+          <t>149872146146</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Motherboard Group Join</t>
+          <t>Exicom Mahindra Treo E Rickshaw Charger Maintenance Service</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Gigabyte Motherboard</t>
+          <t>E Vehicles Repair and Maintenance Services</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>{"Brand":"Gigabyte"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.61).</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>27600782988</t>
+          <t>2854439962173</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Motherboard Group Join</t>
+          <t>Exicom Mahindra Treo E Rickshaw Charger Maintenance Service</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2022/11/QC/JQ/IW/62590101/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/7/435140471/CL/JT/RT/225431338/mahindra-treo-e-rickshaw-charger-repair-service.jpg</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>{"Brand":"Gigabyte"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>149769695352</t>
+          <t>149835766434</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gopro Hero 7 Black (used)</t>
+          <t>Kitchen Accessories</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GoPro Action Camera</t>
+          <t>Kitchen Fittings</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece","Resolution":"12MP","Why do you need this":"For Business Use"}</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"I am interested in":"Kitchen Fittings","Quantity":"3","Quantity Unit":"Piece","Type of Requirement":"Sample Only"}</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.54). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.85).</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2851733684573</t>
+          <t>24590918688</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Gopro Hero 7 Black (Used)</t>
+          <t>HETTICH LIFT UP HALF FOLD</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2023/7/323674298/ID/CW/CA/59750781/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/1/376162113/PJ/PK/RJ/45012959/hettich-lift-up-half-fold.jpg</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"piece","Resolution":"12MP","Why do you need this":"For Business Use"}</t>
+          <t>{"I am interested in":"Kitchen Fittings","Quantity":"3","Quantity Unit":"Piece","Type of Requirement":"Sample Only"}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>149748572895</t>
+          <t>149833734585</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ghar Shop Magic Shop</t>
+          <t>Tata Lpt 407</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Bath Soaps</t>
+          <t>TATA Truck</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>{"Quantity":"3","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.1). LLM fallback failed: HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>{"Model":"407"}</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2855746515662</t>
+          <t>20929090448</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ghar Shop Magic Shop</t>
+          <t>Tata LPT 407</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2025/2/486861013/DB/AV/QP/161582673/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/MF/UM/EO/SELLER-49784604/tata-lpt-407.jpg</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{"Quantity":"3","Quantity Unit":"Piece"}</t>
+          <t>{"Model":"407"}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>149784918263</t>
+          <t>149825908234</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mixer Grinder Spare Part</t>
+          <t>Stranger Spb 8k</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mixer Grinder Spare Parts</t>
+          <t>Stranger PA Amplifier</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>{"Bush Type":"411","Compatibility":"Philips","Part Name":"Chutney Jar","Quantity":"2","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>{"Buyer Filled Details":"4000.W","Model Name":"4000","Origin":"Kolkata","Quantity":"1","Quantity Unit":"Piece"}</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>title_mcat_mismatch</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.98).</t>
+          <t>Title describes a speaker, mcat lists an amplifier.</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.98</v>
+        <v>0.5</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2856752450997</t>
+          <t>2855743319597</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Mixer Grinder Motor Coupler</t>
+          <t>Stranger Spb 8K</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2025/6/519733307/SX/CP/RI/13373616/whatsapp-image-2025-06-07-at-11-48-17-am.jpeg</t>
+          <t>http://5.imimg.com/data5/IOS/Default/2025/2/486709995/SU/DH/ZV/6616321/product-jpeg.png</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>{"Bush Type":"411","Compatibility":"Philips","Part Name":"Chutney Jar","Quantity":"2","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"4000.W","Model Name":"4000","Origin":"Kolkata","Quantity":"1","Quantity Unit":"Piece"}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>149771866146</t>
+          <t>149821046459</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>60acr Jhatka Machine 3 Year Warranty</t>
+          <t>SONY Dav Dz340 Home Theater</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Solar Zatka Machine</t>
+          <t>Sony Home Theater System</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>{"Area Coverage":"Up to 40 Acres","Operation Mode":"Solar &amp; Battery","Output Voltage":"10 kV","Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Channel":"5.1"}</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.36). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.75).</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>26953621862</t>
+          <t>24944808730</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>60acr Jhatka Machine 3 Year Warranty</t>
+          <t>SONY DAV DZ340 Home Theater</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2022/9/CR/ZK/BK/39164893/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2026/6/617427463/WN/UI/RT/29314320/product.jpg</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"Area Coverage":"Up to 40 Acres","Operation Mode":"Solar &amp; Battery","Output Voltage":"10 kV","Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Channel":"5.1"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>149775187246</t>
+          <t>149808093146</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tece Flush Plate</t>
+          <t>Splendor Modified Tail Light</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Flush Plate</t>
+          <t>Automotive Tail Lamps</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>{"Placement":"Right","Quantity":"1","Quantity Unit":"Piece","Scooter Brand":"Hero","Vehicle Brand":"Honda","Vehicle Model":"2025"}</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>isq_filled_title_mismatch</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.84).</t>
+          <t>SCOOTER_BRAND and VEHICLE_BRAND do not match title Splendor.</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2856741092648</t>
+          <t>2857773305888</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Tece Flush Plate</t>
+          <t>Splendor Modified Tail Light</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/6/519201711/ZJ/GK/XN/77803191/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2025/10/555698066/HF/QZ/HA/187988245/prod-20251029-0504325888852409927246734-jpg.jpg</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Piece"}</t>
+          <t>{"Placement":"Right","Quantity":"1","Quantity Unit":"Piece","Scooter Brand":"Hero","Vehicle Brand":"Honda","Vehicle Model":"2025"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>149754092952</t>
+          <t>149809750763</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bajaj Auto Mudguard Packing</t>
+          <t>Wholesale Second Hand Mobile Phones</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Three Wheeler Mudguard</t>
+          <t>Used Mobile Phones</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Buyer wants to use the mudguard for a car.","Quantity":"2","Quantity Unit":"Piece","Three Wheeler Brand":"Bajaj"}</t>
+          <t>{"Brand":"Vivo","Condition":"Demo Unit","Internal Storage":"128 GB"}</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.65).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2850801176548</t>
+          <t>2852929482655</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Bajaj Auto Mudguard Packing</t>
+          <t>Wholesale Second Hand Mobile Phones</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2023/4/300864006/AX/RF/RC/143756784/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2023/11/363566812/DT/YK/JK/117383913/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Buyer wants to use the mudguard for a car.","Quantity":"2","Quantity Unit":"Piece","Three Wheeler Brand":"Bajaj"}</t>
+          <t>{"Brand":"Vivo","Condition":"Demo Unit","Internal Storage":"128 GB"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>149801758563</t>
+          <t>149833292875</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cloth Drying Stand Plastic and Steel Parts Set</t>
+          <t>Tower Fan Spare Parts</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cloth Drying Stand</t>
+          <t>Fan Parts</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>{"Design Type":"Tower","Features":"With wheels","Material":"Plastic and Steel","Quantity":"1","Quantity Unit":"piece"}</t>
+          <t>{"Finish and Color":"Black","Material":"Plastic","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Repair/Service"}</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.84).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.63).</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2850864710797</t>
+          <t>2857080029797</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Cloth Drying Stand Plastic Parts Set</t>
+          <t>Tower Fan Spare Parts</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2026/7/630803213/SC/XP/ZR/188447879/cloth-drying-stand-plastic-parts-set.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/7/529857242/IO/EY/AA/7283415/blue-tower-fan.jpeg</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"Design Type":"Tower","Features":"With wheels","Material":"Plastic and Steel","Quantity":"1","Quantity Unit":"piece"}</t>
+          <t>{"Finish and Color":"Black","Material":"Plastic","Quantity":"1","Quantity Unit":"Piece","Usage/Application":"Repair/Service"}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>149766675713</t>
+          <t>149824829795</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CRE Mushroom Compost Unit</t>
+          <t>Urea Filter Bs-6, Tata</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mushroom Farming Services</t>
+          <t>TATA Truck Spare Parts</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>{"Bag Capacity":"3000 Bags","Mushroom Type":"Button","Service Type":"Mushroom Project"}</t>
+          <t>{"Buyer Filled Details":"Truck / Bus","Quantity":"2","Quantity Unit":"Piece","Vehicle Type":"Truck / Bus"}</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.7).</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>0.7</v>
+        <v>0.22</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2858013612655</t>
+          <t>2856323849630</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>CRE Mushroom Compost Unit</t>
+          <t>Urea Filter BS-6, Tata</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ANDROID/Default/2025/11/563443518/EQ/JL/DX/6284511/product-jpeg.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2025/4/500831049/KQ/OB/MF/17470917/urea-filter-prima-euro-6.webp</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{"Bag Capacity":"3000 Bags","Mushroom Type":"Button","Service Type":"Mushroom Project"}</t>
+          <t>{"Buyer Filled Details":"Truck / Bus","Quantity":"2","Quantity Unit":"Piece","Vehicle Type":"Truck / Bus"}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>149775461834</t>
+          <t>149857177995</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Roots Bajrangi</t>
+          <t>LITHIUM Battery Hx 6000mah 3.6v Ev Cell</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Roots Horn</t>
+          <t>Battery Cell</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Bajarangi roots air horn 24 Volt's","Material Grade":"Budget","Quantity":"7000","Quantity Unit":"Piece"}</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Buyer Filled Details":"6000 mah 4 p","Voltage":"3.6 V"}</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.53). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.78).</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2854199489988</t>
+          <t>2853244297948</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Roots Bajrangi</t>
+          <t>LITHIUM BATTERY HX 6000MAH 3.2V EV CELL</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/IOS/Default/2024/6/424152697/XV/XY/FC/204870392/product-jpeg.png</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2024/2/393255513/JD/FV/WA/85101866/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"Bajarangi roots air horn 24 Volt's","Material Grade":"Budget","Quantity":"7000","Quantity Unit":"Piece"}</t>
+          <t>{"Buyer Filled Details":"6000 mah 4 p","Voltage":"3.6 V"}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>149750411259</t>
+          <t>149869400395</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Agriculture Plastic Sprayer Pump Body</t>
+          <t>Basumoti Banskathi Rice 26kg</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Agricultural Sprayer Component</t>
+          <t>Basmati Rice</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"Component Type":"Sprayer Gun","Material":"Plastic","Quantity":"2","Quantity Unit":"Piece","Usage/Application":"Manufacturing","Used For Sprayer":"Battery Sprayer"}</t>
+          <t>{"Packaging Size":"26 kg","Quantity":"26","Quantity Unit":"Kg"}</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.79).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.81).</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2850439790730</t>
+          <t>2853933790055</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Agriculture Battery Sprayer Pump Body</t>
+          <t>Basumoti Banskathi Rice 26kg</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/3/ZI/FH/RP/134688330/20-l-body.png</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/412117083/YB/GH/GW/89705051/banskathi-26kg.png</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>{"Component Type":"Sprayer Gun","Material":"Plastic","Quantity":"2","Quantity Unit":"Piece","Usage/Application":"Manufacturing","Used For Sprayer":"Battery Sprayer"}</t>
+          <t>{"Packaging Size":"26 kg","Quantity":"26","Quantity Unit":"Kg"}</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>149785309259</t>
+          <t>149872893646</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Online Store Items</t>
+          <t>Goree Whitening Soap</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Plastic Animal Toy</t>
+          <t>Skin Whitening Soap</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Piece","Why do you need this":"For Reselling"}</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Active Ingredient":"Vitamin C","Buyer Filled Details":"Bar, Cream","Product Form":"Gel","Quantity":"200","Quantity Unit":"Piece","Weight":"50 g"}</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.31). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.8).</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2855141091233</t>
+          <t>2855526804730</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Reptile Animal Figurine Toys, 12pcs Reptile Animal Figurine Toys Set?cold Blooded Amphibians Desert Animal Figures Set, With Komodo Dragon Lizard Snake Chameleon Toy Birthday Gift Party Favor For Kids Toddlers</t>
+          <t>Goree Whitening Soap</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/ECOM/Default/2024/10/458695589/EN/OS/TM/234139847/1-6f0eec6e-5f8c-49e3-b616-136ae5ddd480.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/12/476013609/UB/JI/TX/125636981/goree-whitening-soap.jpg</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>{"Quantity":"1","Quantity Unit":"Piece","Why do you need this":"For Reselling"}</t>
+          <t>{"Active Ingredient":"Vitamin C","Buyer Filled Details":"Bar, Cream","Product Form":"Gel","Quantity":"200","Quantity Unit":"Piece","Weight":"50 g"}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>149797918652</t>
+          <t>149868447334</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portable Mini Fridge</t>
+          <t>Single Phase Servo Voltage Stabilizer</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mini Fridge</t>
+          <t>Servo Voltage Stabilizer</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6120,26 +5988,26 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BI Layer Approved: High semantic similarity match (0.95).</t>
+          <t>BI Layer Approved: High semantic similarity match (0.77).</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2850954340930</t>
+          <t>2853436017630</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Portable Mini Fridge</t>
+          <t>Single Phase Servo Voltage Stabilizer</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/4/303362467/HG/WE/LM/86612620/71a-zv1sxhl-sl1490-.jpg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2024/2/388719135/IO/OA/NE/209790761/single-phase-servo-stabilizer.jpeg</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6151,179 +6019,171 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>149746204163</t>
+          <t>149815205867</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Google Pixel 4a 5g 128gb (unlocked) - Used</t>
+          <t>Transformer Extension Stud</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Google Pixel Mobile Phone</t>
+          <t>Transformer Parts</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"google pixel 4a","Condition":"Used","Internal Storage":"128 GB","Network Tech":"4G","Quantity":"3500","Quantity Unit":"piece"}</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>title_mcat_mismatch</t>
-        </is>
-      </c>
+          <t>{"Diameter":"16 mm","Quantity":"3","Quantity Unit":"Piece","Type of Requirement":"Sample Only"}</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.55). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>BI Layer Approved: High semantic similarity match (0.76).</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2850530296588</t>
+          <t>9904846255</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Google Pixel 4a 5G 128GB (Unlocked) - Used</t>
+          <t>Transformer Extension Stud</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2023/3/293715056/DK/YH/BK/184984620/img-8931.jpg</t>
+          <t>http://4.imimg.com/data4/JG/SH/MY-3253680/plc-control-panel.jpg</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>{"Buyer Filled Details":"google pixel 4a","Condition":"Used","Internal Storage":"128 GB","Network Tech":"4G","Quantity":"3500","Quantity Unit":"piece"}</t>
+          <t>{"Diameter":"16 mm","Quantity":"3","Quantity Unit":"Piece","Type of Requirement":"Sample Only"}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>149797482134</t>
+          <t>149821890659</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kyocera Taskalfa 2551ci Multifunction Printer</t>
+          <t>CAS 584-42-9 Alizarin Yellow Gg</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Kyocera Multifunction Printer</t>
+          <t>Pigment Yellow</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"Printing Color":"Color","Supported Paper Size":"A3"}</t>
+          <t>{"Purity":"Greater than 99%","Quantity":"5","Quantity Unit":"kg"}</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>BI Layer Approved: High semantic similarity match (0.94).</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>21019943312</t>
+          <t>2852930433633</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Kyocera Taskalfa 2551ci Multifunction Printer</t>
+          <t>CAS 584-42-9 Alizarin Yellow GG</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2024/4/412680921/ZF/GD/TP/71162214/kyocera-taskalfa-2551ci-multifunction-printer.jpeg</t>
+          <t>http://5.imimg.com/data5/SELLER/Default/2023/11/363600947/HF/NB/PE/202780531/cas-584-42-9-alizarin-yellow-gg.jpg</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>{"Printing Color":"Color","Supported Paper Size":"A3"}</t>
+          <t>{"Purity":"Greater than 99%","Quantity":"5","Quantity Unit":"kg"}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>149780429563</t>
+          <t>149817287413</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Asuran Detergent Soap</t>
+          <t>Baoyu Gt 180</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Detergent Cake</t>
+          <t>Computerized Sewing Machine</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"Quantity":"2","Quantity Unit":"Box"}</t>
+          <t>{"Brand":"Jack","Machine Type":"Single Needle","Model Name":"F5"}</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>title_mcat_mismatch</t>
+          <t>isq_filled_title_mismatch</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BI Layer Mismatch: Cosine similarity low (0.14). LLM fallback failed: HTTP Error 403: Forbidden</t>
+          <t>Filled brand 'Jack' contradicts title brand 'Baoyu'.</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>25521040548</t>
+          <t>23267976173</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Asuran Detergent Soap</t>
+          <t>Baoyu Gt 180</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>http://5.imimg.com/data5/SELLER/Default/2022/4/OM/EY/CH/82150761/detergent-soap-edit.jpeg</t>
+          <t>http://5.imimg.com/data5/ANDROID/Default/2021/3/NR/NN/OE/3459561/product-jpeg.jpg</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>{"Quantity":"2","Quantity Unit":"Box"}</t>
+          <t>{"Brand":"Jack","Machine Type":"Single Needle","Model Name":"F5"}</t>
         </is>
       </c>
     </row>
